--- a/resources/templates/standard/A6200-03.xlsx
+++ b/resources/templates/standard/A6200-03.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>분임조 활동 회의록</t>
   </si>
@@ -817,7 +820,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -825,7 +830,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -848,23 +853,23 @@
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD1" s="3"/>
       <c r="AE1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
       <c r="AH1" s="4"/>
       <c r="AI1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4"/>
@@ -1004,7 +1009,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1050,7 +1055,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1073,7 +1078,7 @@
       <c r="T6" s="12"/>
       <c r="U6" s="12"/>
       <c r="V6" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
@@ -1098,7 +1103,7 @@
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1121,7 +1126,7 @@
       <c r="T7" s="12"/>
       <c r="U7" s="12"/>
       <c r="V7" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
@@ -1146,7 +1151,7 @@
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1169,7 +1174,7 @@
       <c r="T8" s="12"/>
       <c r="U8" s="12"/>
       <c r="V8" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
@@ -1194,7 +1199,7 @@
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -1284,7 +1289,7 @@
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -2166,7 +2171,7 @@
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -2256,7 +2261,7 @@
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -2279,7 +2284,7 @@
       <c r="T33" s="11"/>
       <c r="U33" s="11"/>
       <c r="V33" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
